--- a/artfynd/A 54624-2024 artfynd.xlsx
+++ b/artfynd/A 54624-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2056861</v>
+        <v>316110</v>
       </c>
       <c r="B2" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630854.0790415339</v>
+        <v>630884</v>
       </c>
       <c r="R2" t="n">
-        <v>7009631.171207109</v>
+        <v>7009721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>bäckdal granskog</t>
+          <t>blockig äldre granskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # medelålders sälg</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,12 +792,7 @@
         <v>1674212</v>
       </c>
       <c r="B3" t="n">
-        <v>89355</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630856.5683617966</v>
+        <v>630857</v>
       </c>
       <c r="R3" t="n">
-        <v>7009603.255717217</v>
+        <v>7009603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,37 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>316110</v>
+        <v>2056861</v>
       </c>
       <c r="B4" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630883.9045007887</v>
+        <v>630854</v>
       </c>
       <c r="R4" t="n">
-        <v>7009721.398957083</v>
+        <v>7009631</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +971,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blockig äldre granskog</t>
+          <t>bäckdal granskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1040,7 +995,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # medelålders sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 54624-2024 artfynd.xlsx
+++ b/artfynd/A 54624-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316110</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1674212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2056861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>